--- a/books/batch13/B13-001_renovation_allowance_control.xlsx
+++ b/books/batch13/B13-001_renovation_allowance_control.xlsx
@@ -4793,7 +4793,7 @@
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>All-in plan (revised budget + reserve)</t>
+          <t>All-in plan (revised budget + reserve left)</t>
         </is>
       </c>
       <c r="B19" s="16">
@@ -4801,7 +4801,17 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>Contingency drawn to date</t>
+        </is>
+      </c>
+      <c r="B20" s="16">
+        <f>Contingency!$H$2</f>
+        <v/>
+      </c>
+    </row>
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
         <is>
